--- a/assets/csv/faculty.xlsx
+++ b/assets/csv/faculty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64FE24B8-E916-5F4C-9BDB-5197DFB59633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2A0734-194D-0F43-97AF-C8C58154501D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>

--- a/assets/csv/faculty.xlsx
+++ b/assets/csv/faculty.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hassan.491/Library/Mobile Documents/com~apple~CloudDocs/Workstation/bgsa osu website/bgsa-osu.github.io/assets/csv/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2A0734-194D-0F43-97AF-C8C58154501D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44EEFF6-8BA7-FB45-962F-6A438EC996FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="18440" xr2:uid="{9492E0D0-CCC2-E442-BF6F-4DDE557B2EBA}"/>
   </bookViews>
@@ -203,9 +203,6 @@
     <t>Mathematics</t>
   </si>
   <si>
-    <t>ECE</t>
-  </si>
-  <si>
     <t>Mechanical and Aerospace Engineering</t>
   </si>
   <si>
@@ -225,6 +222,9 @@
   </si>
   <si>
     <t xml:space="preserve">Media and Journalism... </t>
+  </si>
+  <si>
+    <t>Electrical and Computer Engineering</t>
   </si>
 </sst>
 </file>
@@ -749,7 +749,7 @@
         <v>46</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -767,7 +767,7 @@
         <v>46</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -783,7 +783,7 @@
         <v>47</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -801,7 +801,7 @@
         <v>48</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -819,7 +819,7 @@
         <v>49</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -837,7 +837,7 @@
         <v>50</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -855,7 +855,7 @@
         <v>46</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -873,7 +873,7 @@
         <v>51</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -891,7 +891,7 @@
         <v>49</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -909,7 +909,7 @@
         <v>52</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -923,7 +923,7 @@
       <c r="D15" s="6"/>
       <c r="E15" s="8"/>
       <c r="F15" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6">
